--- a/02-精益培训/05-记录追踪/02-技能矩阵追踪表.xlsx
+++ b/02-精益培训/05-记录追踪/02-技能矩阵追踪表.xlsx
@@ -95,7 +95,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -122,11 +122,20 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="001F3A5F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -150,6 +159,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -533,7 +543,13 @@
           <t>02-技能矩阵追踪表</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+      <c r="E1" s="11" t="n"/>
+      <c r="F1" s="11" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -541,6 +557,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -548,6 +565,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -555,6 +573,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
@@ -562,6 +581,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -569,6 +589,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -576,13 +597,15 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>3. 紧固件相关技能项列表</t>
-        </is>
-      </c>
-    </row>
+          <t>3. 产品相关技能项列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
@@ -590,6 +613,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
@@ -597,6 +621,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
@@ -604,6 +629,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
@@ -611,6 +637,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
@@ -618,6 +645,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
@@ -625,6 +653,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
@@ -632,6 +661,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
@@ -639,6 +669,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
@@ -646,6 +677,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
@@ -653,6 +685,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
@@ -660,6 +693,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
@@ -667,6 +701,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
@@ -674,6 +709,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
@@ -681,6 +717,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
@@ -688,6 +725,7 @@
         </is>
       </c>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
@@ -695,6 +733,7 @@
         </is>
       </c>
     </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
@@ -702,6 +741,7 @@
         </is>
       </c>
     </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
@@ -709,6 +749,7 @@
         </is>
       </c>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
@@ -730,6 +771,7 @@
         </is>
       </c>
     </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
@@ -737,6 +779,7 @@
         </is>
       </c>
     </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
@@ -744,6 +787,7 @@
         </is>
       </c>
     </row>
+    <row r="60"/>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
@@ -751,6 +795,7 @@
         </is>
       </c>
     </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
@@ -786,6 +831,7 @@
         </is>
       </c>
     </row>
+    <row r="68"/>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
@@ -793,6 +839,7 @@
         </is>
       </c>
     </row>
+    <row r="70"/>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
@@ -800,6 +847,7 @@
         </is>
       </c>
     </row>
+    <row r="72"/>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
@@ -828,6 +876,7 @@
         </is>
       </c>
     </row>
+    <row r="77"/>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
@@ -835,6 +884,7 @@
         </is>
       </c>
     </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
@@ -863,6 +913,7 @@
         </is>
       </c>
     </row>
+    <row r="84"/>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
@@ -870,6 +921,7 @@
         </is>
       </c>
     </row>
+    <row r="86"/>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
@@ -1458,12 +1510,12 @@
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>冷镦操作</t>
+          <t>机加工操作</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>操作冷镦机进行螺栓/螺母成型</t>
+          <t>操作机加工设备进行工件/工件成型</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1527,12 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>搓丝操作</t>
+          <t>精加工操作</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>操作搓丝机进行螺纹加工</t>
+          <t>操作精加工设备进行精加工</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1600,7 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>安装和调整冲压/搓丝模具</t>
+          <t>安装和调整冲压/精加工模具</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1722,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>使用通止规等检测螺纹精度</t>
+          <t>使用量规等检测螺纹精度</t>
         </is>
       </c>
     </row>
